--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487465_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487465_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2586</v>
+        <v>2.6055</v>
       </c>
       <c r="E2" t="n">
-        <v>0.753</v>
+        <v>-0.8843</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5056</v>
+        <v>3.4898</v>
       </c>
       <c r="G2" t="n">
         <v>2.0163</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7632</v>
+        <v>1.1101</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2825</v>
+        <v>0.6452</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4807</v>
+        <v>0.4649</v>
       </c>
       <c r="V2" t="n">
         <v>0.06660000000000001</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.151</v>
+        <v>2.5695</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0603</v>
+        <v>0.265</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0907</v>
+        <v>2.3045</v>
       </c>
       <c r="G3" t="n">
         <v>1.7355</v>
@@ -688,13 +688,13 @@
         <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9555</v>
+        <v>-0.537</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7128</v>
+        <v>-0.5082</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2427</v>
+        <v>-0.0288</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0841</v>
+        <v>2.2804</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8594</v>
+        <v>1.6547</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2247</v>
+        <v>0.6257</v>
       </c>
       <c r="G4" t="n">
         <v>3.5255</v>
@@ -766,13 +766,13 @@
         <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4873</v>
+        <v>-0.291</v>
       </c>
       <c r="T4" t="n">
-        <v>0.414</v>
+        <v>0.2094</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9013</v>
+        <v>-0.5004</v>
       </c>
       <c r="V4" t="n">
         <v>-1.15</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9510999999999999</v>
+        <v>2.2464</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5631</v>
+        <v>0.3579</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5143</v>
+        <v>1.8885</v>
       </c>
       <c r="G5" t="n">
         <v>1.9883</v>
@@ -844,13 +844,13 @@
         <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4955</v>
+        <v>-0.2003</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0692</v>
+        <v>-0.1482</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4263</v>
+        <v>-0.052</v>
       </c>
       <c r="V5" t="n">
         <v>0.06660000000000001</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. REIRIZ MENDEZ</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4171</v>
+        <v>0.4552</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.838</v>
+        <v>0.4149</v>
       </c>
       <c r="F6" t="n">
-        <v>1.255</v>
+        <v>0.0403</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0208</v>
+        <v>-0.1544</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1256</v>
+        <v>-0.0483</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1465</v>
+        <v>-0.106</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4385</v>
+        <v>0.6425</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1225</v>
+        <v>-0.0494</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5610000000000001</v>
+        <v>0.6919</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4177</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0031</v>
+        <v>0.001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4145</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7834</v>
+        <v>0.9792</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7834</v>
+        <v>0.9792</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3204</v>
+        <v>-0.3696</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2664</v>
+        <v>-0.2276</v>
       </c>
       <c r="U6" t="n">
-        <v>0.054</v>
+        <v>-0.142</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>D. REIRIZ MENDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0122</v>
+        <v>0.3728</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1079</v>
+        <v>-1.0426</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1201</v>
+        <v>1.4154</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1544</v>
+        <v>-0.0208</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0483</v>
+        <v>0.1256</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.106</v>
+        <v>-0.1465</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6425</v>
+        <v>-0.4385</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0494</v>
+        <v>0.1225</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6919</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7969000000000001</v>
+        <v>0.4177</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001</v>
+        <v>0.0031</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.4145</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.837</v>
+        <v>0.2761</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5346</v>
+        <v>0.0618</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3024</v>
+        <v>0.2144</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4148</v>
+        <v>-0.3743</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8064</v>
+        <v>-3.1135</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3916</v>
+        <v>2.7391</v>
       </c>
       <c r="G8" t="n">
         <v>-3.1734</v>
@@ -1078,13 +1078,13 @@
         <v>2.546</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0718</v>
+        <v>-0.0313</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3241</v>
+        <v>0.017</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3959</v>
+        <v>-0.0484</v>
       </c>
       <c r="V8" t="n">
         <v>0.2844</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0287</v>
+        <v>-0.5659</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2335</v>
+        <v>-0.8242</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2048</v>
+        <v>0.2582</v>
       </c>
       <c r="G9" t="n">
         <v>1.6751</v>
@@ -1156,13 +1156,13 @@
         <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8248</v>
+        <v>-0.362</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7722</v>
+        <v>-0.3629</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0526</v>
+        <v>0.0009</v>
       </c>
       <c r="V9" t="n">
         <v>0.2754</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0766</v>
+        <v>-1.5974</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.886</v>
+        <v>-3.193</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8094</v>
+        <v>1.5956</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6448</v>
@@ -1234,13 +1234,13 @@
         <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6649</v>
+        <v>0.1441</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0288</v>
+        <v>-0.2782</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6361</v>
+        <v>0.4223</v>
       </c>
       <c r="V10" t="n">
         <v>0.6659</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0694</v>
+        <v>-4.7319</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.6112</v>
+        <v>-6.7925</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5417</v>
+        <v>2.0606</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5829</v>
@@ -1312,13 +1312,13 @@
         <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1649</v>
+        <v>0.1726</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2474</v>
+        <v>-0.4288</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0825</v>
+        <v>0.6014</v>
       </c>
       <c r="V11" t="n">
         <v>0.3995</v>
@@ -1345,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.260199999999999</v>
+        <v>3.2603</v>
       </c>
       <c r="E12" t="n">
         <v>-13.1576</v>
@@ -1390,13 +1390,13 @@
         <v>12.73</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.08830000000000021</v>
+        <v>-0.08829999999999985</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0204</v>
+        <v>-1.0205</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9321000000000002</v>
+        <v>0.9323000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-0.05749999999999994</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>M. RODRIGUEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3445</v>
+        <v>2.0755</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2455</v>
+        <v>1.5484</v>
       </c>
       <c r="F13" t="n">
-        <v>3.099</v>
+        <v>0.527</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2849</v>
+        <v>1.3157</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3966</v>
+        <v>0.866</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6815</v>
+        <v>0.4498</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5496</v>
+        <v>1.6408</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2231</v>
+        <v>0.3879</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7727000000000001</v>
+        <v>1.2529</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8345</v>
+        <v>-0.325</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6197</v>
+        <v>0.4781</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.4542</v>
+        <v>-0.8031</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.546</v>
+        <v>1.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5824</v>
+        <v>-0.4154</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2615</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3208</v>
+        <v>-0.323</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3239</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.06660000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ ALVAREZ</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7371</v>
+        <v>1.9487</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3437</v>
+        <v>-1.8498</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3934</v>
+        <v>3.7985</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3157</v>
+        <v>1.6998</v>
       </c>
       <c r="H14" t="n">
-        <v>0.866</v>
+        <v>1.5278</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4498</v>
+        <v>0.172</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6408</v>
+        <v>0.7156</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3879</v>
+        <v>0.706</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2529</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.325</v>
+        <v>0.9842</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4781</v>
+        <v>0.8218</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8031</v>
+        <v>0.1624</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1751</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7537</v>
+        <v>0.104</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.297</v>
+        <v>-0.4111</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4567</v>
+        <v>0.5151</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.7325</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.7325</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>C. MONTERO MECA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3171</v>
+        <v>1.7921</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.6685</v>
+        <v>0.3996</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9857</v>
+        <v>1.3925</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6998</v>
+        <v>0.8042</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5278</v>
+        <v>2.3348</v>
       </c>
       <c r="I15" t="n">
-        <v>0.172</v>
+        <v>-1.5306</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7156</v>
+        <v>1.7814</v>
       </c>
       <c r="K15" t="n">
-        <v>0.706</v>
+        <v>1.8526</v>
       </c>
       <c r="L15" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.0712</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9842</v>
+        <v>-0.9771</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8218</v>
+        <v>0.4822</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1624</v>
+        <v>-1.4594</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5668</v>
+        <v>2.3502</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5276</v>
+        <v>-0.4246</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2298</v>
+        <v>-0.4441</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7022</v>
+        <v>0.0194</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7325</v>
+        <v>1.2166</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. RUMSHA</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1969</v>
+        <v>1.5147</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9701</v>
+        <v>-0.6755</v>
       </c>
       <c r="F16" t="n">
-        <v>2.167</v>
+        <v>2.1902</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4452</v>
+        <v>-0.2849</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8133</v>
+        <v>0.3966</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2584</v>
+        <v>-0.6815</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5995</v>
+        <v>0.5496</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.9736</v>
+        <v>-0.2231</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3741</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0446</v>
+        <v>-0.8345</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1603</v>
+        <v>0.6197</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1157</v>
+        <v>-1.4542</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1958</v>
+        <v>1.3709</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1751</v>
+        <v>2.546</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2217</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2745</v>
+        <v>0.3405</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0528</v>
+        <v>0.412</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6659</v>
+        <v>-0.3239</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6659</v>
+        <v>-0.3905</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. MONTERO MECA</t>
+          <t>G. RUMSHA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.4675</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6238</v>
+        <v>-1.9935</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1786</v>
+        <v>2.461</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8042</v>
+        <v>0.4452</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3348</v>
+        <v>-0.8133</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5306</v>
+        <v>1.2584</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7814</v>
+        <v>-0.5995</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8526</v>
+        <v>-1.9736</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0712</v>
+        <v>1.3741</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9771</v>
+        <v>1.0446</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4822</v>
+        <v>1.1603</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4594</v>
+        <v>-0.1157</v>
       </c>
       <c r="P17" t="n">
         <v>0.1958</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6618</v>
+        <v>0.4924</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4674</v>
+        <v>0.2511</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1944</v>
+        <v>0.2413</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2166</v>
+        <v>-0.6659</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2166</v>
+        <v>-0.6659</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5282</v>
+        <v>-1.4655</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8315</v>
+        <v>-2.0361</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3033</v>
+        <v>0.5706</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9358</v>
@@ -1858,13 +1858,13 @@
         <v>2.1543</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3629</v>
+        <v>-0.3002</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0435</v>
+        <v>-0.2482</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3194</v>
+        <v>-0.052</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2088</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1222</v>
+        <v>-1.8106</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.88</v>
+        <v>-2.6753</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7578</v>
+        <v>0.8648</v>
       </c>
       <c r="G19" t="n">
         <v>1.0307</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4569</v>
+        <v>-0.1453</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4158</v>
+        <v>-0.2111</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.041</v>
+        <v>0.0659</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5417</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8475</v>
+        <v>-3.208</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5391</v>
+        <v>-2.8461</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3084</v>
+        <v>-0.3619</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1606</v>
@@ -2014,13 +2014,13 @@
         <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5101</v>
+        <v>0.1497</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3852</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1249</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0.3905</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9129</v>
+        <v>-4.5746</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.4941</v>
+        <v>-6.2894</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5812</v>
+        <v>1.7149</v>
       </c>
       <c r="G21" t="n">
         <v>-5.279</v>
@@ -2092,13 +2092,13 @@
         <v>2.546</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4632</v>
+        <v>-0.1248</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3999</v>
+        <v>-0.1953</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.06320000000000001</v>
+        <v>0.0704</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5417</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.260299999999999</v>
+        <v>-3.2602</v>
       </c>
       <c r="E22" t="n">
-        <v>-16.4179</v>
+        <v>-16.4177</v>
       </c>
       <c r="F22" t="n">
         <v>13.1576</v>
@@ -2146,7 +2146,7 @@
         <v>-2.5825</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3800999999999997</v>
+        <v>-0.3800999999999999</v>
       </c>
       <c r="L22" t="n">
         <v>-2.2024</v>
@@ -2170,19 +2170,19 @@
         <v>14.6886</v>
       </c>
       <c r="S22" t="n">
-        <v>0.08809999999999946</v>
+        <v>0.08829999999999993</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9321999999999999</v>
+        <v>-0.9323</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0204</v>
+        <v>1.0206</v>
       </c>
       <c r="V22" t="n">
-        <v>0.05759999999999976</v>
+        <v>0.05759999999999998</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.1727000000000001</v>
+        <v>-0.1727000000000002</v>
       </c>
       <c r="X22" t="n">
         <v>0.2303</v>
